--- a/Result/profitability/2504.xlsx
+++ b/Result/profitability/2504.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7137499999999999</v>
+        <v>0.7187499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>24.4925</v>
+        <v>24.5375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6425</v>
+        <v>0.6375</v>
       </c>
       <c r="N3" t="n">
-        <v>22.63375</v>
+        <v>22.50875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.57625</v>
+        <v>0.5837499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>20.65</v>
+        <v>20.5725</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4774999999999999</v>
+        <v>0.4649999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>17.97625</v>
+        <v>17.695</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3774999999999999</v>
+        <v>0.365</v>
       </c>
       <c r="N6" t="n">
-        <v>16.51875</v>
+        <v>15.9825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2899999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="N7" t="n">
-        <v>13.87375</v>
+        <v>13.51625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2</v>
+        <v>0.2087499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>11.66125</v>
+        <v>11.44625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.11875</v>
       </c>
       <c r="N9" t="n">
-        <v>9.635</v>
+        <v>9.635000000000002</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5217</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3917</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1035</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.85%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>122</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1157</v>
+      </c>
+      <c r="K75" t="n">
+        <v>911</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7887499999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.4475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.720000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06461307287753582</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1149425287356322</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08287292817679559</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
